--- a/tests/fixtures/extract_corpus_v2/dev/bundle_vv40_cfd_001/extracted.xlsx
+++ b/tests/fixtures/extract_corpus_v2/dev/bundle_vv40_cfd_001/extracted.xlsx
@@ -490,6 +490,11 @@
         <t>[Extract] | Confidence: 50%</t>
       </text>
     </comment>
+    <comment ref="K3" authorId="0" shapeId="0">
+      <text>
+        <t>[Extract] | Confidence: 50%</t>
+      </text>
+    </comment>
     <comment ref="L3" authorId="0" shapeId="0">
       <text>
         <t>[Extract] | Confidence: 50%</t>
@@ -691,6 +696,11 @@
       </text>
     </comment>
     <comment ref="F5" authorId="0" shapeId="0">
+      <text>
+        <t>[Extract] | Confidence: 50%</t>
+      </text>
+    </comment>
+    <comment ref="G5" authorId="0" shapeId="0">
       <text>
         <t>[Extract] | Confidence: 50%</t>
       </text>
@@ -1418,12 +1428,12 @@
       </c>
       <c r="B3" s="39" t="inlineStr">
         <is>
-          <t>CFD of centrifugal LVAD for pressure-flow (H-Q map) and blood damage (NIH) predictions to inform firmware guard bands and design screening prior to first-in-human evaluation</t>
+          <t>CFD of centrifugal LVAD for pressure-flow (H-Q map) and blood damage (NIH) predictions</t>
         </is>
       </c>
       <c r="C3" s="39" t="inlineStr">
         <is>
-          <t>A CFD model of a rotary blood pump (centrifugal LVAD, Rev E) is used to predict the hydraulic head-flow map across 2–6 L/min and 2400–3600 rpm, and to rank design variants by normalized index of hemolysis (NIH). The H-Q map seeds firmware speed-limiter curves and battery sizing; the NIH estimate prioritizes benchtop blood-loop tests and gates design iteration. Blood rheology is Carreau–Yasuda at Hct 40%, temperature 37 °C. Validation was performed against ISO 7199 hydraulic rig tests and ASTM F1841 bovine blood-loop hemolysis tests on the same Rev E pump.</t>
+          <t>CFD model of a rotary centrifugal LVAD (Rev E) used to predict the hydraulic head-flow map across 2–6 L/min and 2400–3600 rpm, and to rank design variants by normalized index of hemolysis (NIH). Results inform firmware speed-limiter curves, battery sizing, and prioritization of ISO 7199 bench tests prior to first-in-human evaluation.</t>
         </is>
       </c>
       <c r="D3" s="39" t="inlineStr">
@@ -1461,9 +1471,9 @@
           <t>Date of this assessment (YYYY-MM-DD)</t>
         </is>
       </c>
-      <c r="K3" s="22" t="inlineStr">
-        <is>
-          <t>DOI, report number, or URI</t>
+      <c r="K3" s="39" t="inlineStr">
+        <is>
+          <t>report.md (Credibility Assessment Report — CFD of a Centrifugal LVAD for Pressure–Flow and Blood Damage Predictions, Model ID LVAD-CFD-hem_v3.4, Git tag 3.4.7, dated 2026-08-06)</t>
         </is>
       </c>
       <c r="L3" s="40" t="inlineStr">
@@ -2059,7 +2069,7 @@
       </c>
       <c r="B3" s="39" t="inlineStr">
         <is>
-          <t>Hydraulic H-Q map accuracy requirement</t>
+          <t>H-Q Map Accuracy Requirement</t>
         </is>
       </c>
       <c r="C3" s="22" t="inlineStr">
@@ -2069,7 +2079,7 @@
       </c>
       <c r="D3" s="39" t="inlineStr">
         <is>
-          <t>CFD-predicted head must agree with rig measurements to within 5% per operating point and overall MAPE &lt; 4% across the 2–6 L/min, 2400–3600 rpm envelope, with fine-mesh GCI &lt; 3%; used to set firmware speed-limiter curves and battery sizing margins.</t>
+          <t>Predicted head must agree with physical rig measurements to within 5% pointwise and MAPE &lt; 4% across the full operating window (2–6 L/min, 2400–3600 rpm); numerical GCI for head &lt; 3%; used to set firmware guard bands and battery sizing margins.</t>
         </is>
       </c>
       <c r="E3" s="22" t="inlineStr">
@@ -2091,13 +2101,13 @@
       </c>
       <c r="B4" s="41" t="inlineStr">
         <is>
-          <t>NIH ranking and magnitude requirement</t>
+          <t>NIH Ranking and Magnitude Requirement</t>
         </is>
       </c>
       <c r="C4" s="24" t="n"/>
       <c r="D4" s="41" t="inlineStr">
         <is>
-          <t>CFD-predicted NIH must show correct monotonic ranking across design variants (Rev D, E, E+) and absolute error &lt; 30% versus blood-loop bench data; used as a screening gate before full ISO 7199 / in vivo testing.</t>
+          <t>CFD-predicted NIH must correctly rank design variants (Rev D, E, E+) and absolute error vs blood-loop bench data must remain &lt; 30%; used as screening tool to prioritize ISO 7199 blood loop testing; not used for direct clinical safety claims.</t>
         </is>
       </c>
       <c r="E4" s="33" t="n"/>
@@ -2111,13 +2121,13 @@
       </c>
       <c r="B5" s="41" t="inlineStr">
         <is>
-          <t>LVAD CFD model (ANSYS CFX/Fluent 2024 R1, hem_v3.4)</t>
+          <t>LVAD CFD Model (LVAD-CFD-hem_v3.4)</t>
         </is>
       </c>
       <c r="C5" s="24" t="n"/>
       <c r="D5" s="41" t="inlineStr">
         <is>
-          <t>Incompressible isothermal Navier–Stokes with MRF/sliding-mesh rotating frame, k-ω SST with curvature correction, Carreau–Yasuda blood rheology, and a power-law hemolysis scalar transport surrogate (Giersiepen/Heuser–Opitz coefficients); poly-prism meshes 7.9–28.6 M cells.</t>
+          <t>Incompressible, isothermal Navier-Stokes with MRF/sliding-mesh rotating frame; k-ω SST with curvature correction; Carreau-Yasuda blood rheology; power-law hemolysis scalar transport (Giersiepen/Heuser-Opitz coefficients); ANSYS CFX 2024 R1 (H-Q) and Fluent 2024 R1 (NIH transient).</t>
         </is>
       </c>
       <c r="E5" s="33" t="n"/>
@@ -2131,13 +2141,13 @@
       </c>
       <c r="B6" s="41" t="inlineStr">
         <is>
-          <t>ISO 7199 hydraulic rig test dataset (Rev E pump)</t>
+          <t>ISO 7199 Hydraulic Rig Dataset</t>
         </is>
       </c>
       <c r="C6" s="24" t="n"/>
       <c r="D6" s="41" t="inlineStr">
         <is>
-          <t>Pressure-rise and flow measurements at 15 operating points (2–6 L/min × 2400/3000/3600 rpm) using water–glycerol at 3.5 cP; Rosemount 3051 transducers (±0.075% span) and Transonic flowmeter (±2%), NIST-traceable calibration.</t>
+          <t>Pressure-flow measurements on LVAD Rev E with water-glycerol at 3.5 cP; 15 operating points across 2400/3000/3600 rpm and 2–6 L/min; Rosemount 3051 transducers (±0.075% span) and Transonic flowmeter (±2%); calibrations traceable to NIST.</t>
         </is>
       </c>
       <c r="E6" s="33" t="n"/>
@@ -2151,13 +2161,13 @@
       </c>
       <c r="B7" s="41" t="inlineStr">
         <is>
-          <t>ASTM F1841 bovine blood-loop hemolysis dataset (Rev E pump)</t>
+          <t>Blood Loop NIH Dataset</t>
         </is>
       </c>
       <c r="C7" s="24" t="n"/>
       <c r="D7" s="41" t="inlineStr">
         <is>
-          <t>Triplicate NIH measurements at 2400 rpm, 3/4/5 L/min for Rev D, E, and E+ variants; bovine blood Hct 38–42%, 37 °C ± 0.2 °C, 2-hour runs; CV 6.1% across triplicates.</t>
+          <t>Bovine blood hemolysis tests at Hct 38–42%, 2400 rpm, 3/4/5 L/min, 2-hour runs; NIH per ASTM F1841; triplicates on separate days; CV 6.1%; temperature 36.8–37.2 °C.</t>
         </is>
       </c>
       <c r="E7" s="33" t="n"/>
@@ -2299,7 +2309,7 @@
     <row r="3" ht="32.8" customHeight="1" s="18">
       <c r="A3" s="39" t="inlineStr">
         <is>
-          <t>Hydraulic H-Q map validation against ISO 7199 rig data</t>
+          <t>Hydraulic H-Q Map Validation</t>
         </is>
       </c>
       <c r="B3" s="39" t="inlineStr">
@@ -2314,12 +2324,12 @@
       </c>
       <c r="D3" s="39" t="inlineStr">
         <is>
-          <t>CFD (Newtonian 3.5 cP, matched to rig fluid) head predictions compared against 15 measured operating points at 2400/3000/3600 rpm and 2–6 L/min. Acceptance criteria declared prior to comparison: pointwise error &lt; 5%, MAPE &lt; 4%.</t>
+          <t>CFD (Newtonian μ = 3.5 cP, CFX MRF) head predictions compared to ISO 7199 rig measurements at 15 operating points spanning 2400–3600 rpm and 2–6 L/min; acceptance criteria declared prior to comparison.</t>
         </is>
       </c>
       <c r="E3" s="39" t="inlineStr">
         <is>
-          <t>ISO 7199 water–glycerol rig measurements (artifacts ARIG-*)</t>
+          <t>ISO 7199 water-glycerol rig test data (artifact series ARIG-*)</t>
         </is>
       </c>
       <c r="F3" s="39" t="inlineStr">
@@ -2329,12 +2339,12 @@
       </c>
       <c r="G3" s="39" t="inlineStr">
         <is>
-          <t>Latin hypercube propagation (300 runs, coarse mesh + GCI correction) yielding 95% head interval [108.2, 112.7] mmHg at 3000 rpm/4 L/min; Sobol' first-order sensitivity indices on GP surrogate (LOO error 1.1%)</t>
+          <t>Latin hypercube sampling (300 runs) on coarse mesh with GCI correction factors; Sobol' variance-based sensitivity; Morris screening; 95% prediction interval reported.</t>
         </is>
       </c>
       <c r="H3" s="39" t="inlineStr">
         <is>
-          <t>MAPE 2.7%; worst-case pointwise error 4.9% (at 2 L/min/2400 rpm); lab repeat variability 1.3% (1σ); fine-mesh GCI 0.9% (95%)</t>
+          <t>MAPE 2.7%; worst-case single-point error 4.9% (2 L/min, 2400 rpm); H-Q slope agreement within 3%; lab repeat variability 1.3% (1σ); 95% CI for head at 3000 rpm/4 L/min: [108.2, 112.7] mmHg.</t>
         </is>
       </c>
       <c r="I3" s="42" t="inlineStr">
@@ -2346,7 +2356,7 @@
     <row r="4" ht="15" customHeight="1" s="18">
       <c r="A4" s="41" t="inlineStr">
         <is>
-          <t>NIH blood damage validation against ASTM F1841 blood-loop data</t>
+          <t>Blood-Loop NIH Validation</t>
         </is>
       </c>
       <c r="B4" s="41" t="inlineStr">
@@ -2357,12 +2367,12 @@
       <c r="C4" s="33" t="n"/>
       <c r="D4" s="41" t="inlineStr">
         <is>
-          <t>Transient sliding-mesh CFD NIH predictions (power-law surrogate, Giersiepen and Heuser–Opitz coefficients) compared against triplicate blood-loop bench measurements for Rev D, E, and E+ at 2400 rpm and 3/4/5 L/min. Acceptance criteria pre-specified: absolute error &lt; 30%, correct design ranking.</t>
+          <t>CFD-predicted NIH (transient sliding-mesh, Giersiepen and Heuser-Opitz coefficient sets) compared to bovine blood-loop bench data at 2400 rpm and 3/4/5 L/min for three design variants (Rev D, E, E+).</t>
         </is>
       </c>
       <c r="E4" s="41" t="inlineStr">
         <is>
-          <t>ASTM F1841 bovine blood-loop NIH triplicates (artifacts ABLD-*)</t>
+          <t>Blood loop NIH measurements per ASTM F1841 (artifact series ABLD-*)</t>
         </is>
       </c>
       <c r="F4" s="41" t="inlineStr">
@@ -2372,12 +2382,12 @@
       </c>
       <c r="G4" s="41" t="inlineStr">
         <is>
-          <t>95% interval [0.026, 0.044] g/100 L from LHC propagation including damage coefficient epistemic spread and GCI correction; LES-informed upper-tail inflation (+10%) for tip-leakage-dominated points; Morris screening + Sobol' (LOO error 9.2% on GP surrogate)</t>
+          <t>95% prediction interval from LHS propagation including literature coefficient spread; model-form uncertainty inflation (+10% upper tail) from LES spot check; calibration sensitivity branch using Rev C data.</t>
         </is>
       </c>
       <c r="H4" s="41" t="inlineStr">
         <is>
-          <t>Bias +24% (baseline Giersiepen); +12% (alternate Heuser–Opitz); correct ranking across three designs; 5/9 test conditions bracketed by CFD 95% interval; time-step error 2.1% (target ≤ 3%)</t>
+          <t>Baseline bias +24% (RMSE 0.010 g/100 L); alternate coefficients bias +12%; correct design ranking in 3/3 variants; 5 of 9 test conditions bracketed by UQ interval; two 5 L/min points marginally exceeded 30% threshold with baseline coefficients; 95% NIH CI at 2400 rpm/4 L/min: [0.026, 0.044] g/100 L vs measured 0.029–0.032 g/100 L.</t>
         </is>
       </c>
       <c r="I4" s="42" t="inlineStr">
@@ -2389,7 +2399,7 @@
     <row r="5" ht="15" customHeight="1" s="18">
       <c r="A5" s="41" t="inlineStr">
         <is>
-          <t>Mesh convergence study (Richardson extrapolation / GCI)</t>
+          <t>Mesh Convergence Study (GCI)</t>
         </is>
       </c>
       <c r="B5" s="41" t="inlineStr">
@@ -2400,23 +2410,27 @@
       <c r="C5" s="33" t="n"/>
       <c r="D5" s="41" t="inlineStr">
         <is>
-          <t>Three-mesh refinement study (7.9M / 14.8M / 28.6M cells) at 3000 rpm, 4 L/min; head values 109.1 / 110.5 / 111.0 mmHg; Richardson-extrapolated value 111.4 mmHg; observed order p ≈ 1.96; GCI computed via Roache's method.</t>
+          <t>Three-mesh (7.9M/14.8M/28.6M cell) refinement study at 3000 rpm/4 L/min; Richardson extrapolation and Roache GCI computed for head; observed spatial order verified.</t>
         </is>
       </c>
       <c r="E5" s="41" t="inlineStr">
         <is>
-          <t>Richardson extrapolation zero-grid-size estimate</t>
+          <t>Richardson extrapolated value (111.4 mmHg)</t>
         </is>
       </c>
       <c r="F5" s="41" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G5" s="33" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G5" s="41" t="inlineStr">
+        <is>
+          <t>Grid Convergence Index (Roache's method, 95% confidence)</t>
+        </is>
+      </c>
       <c r="H5" s="41" t="inlineStr">
         <is>
-          <t>Fine-grid GCI 0.9% (95% confidence); pre-specified target &lt; 3%</t>
+          <t>Head values 109.1/110.5/111.0 mmHg; observed order p ≈ 1.96; fine-grid GCI 0.9% (95%); pre-specified target &lt; 3%.</t>
         </is>
       </c>
       <c r="I5" s="42" t="inlineStr">
@@ -2428,7 +2442,7 @@
     <row r="6" ht="15" customHeight="1" s="18">
       <c r="A6" s="41" t="inlineStr">
         <is>
-          <t>Manufactured solution / numerical code verification</t>
+          <t>Time-Step Sensitivity Study (NIH)</t>
         </is>
       </c>
       <c r="B6" s="41" t="inlineStr">
@@ -2439,12 +2453,12 @@
       <c r="C6" s="33" t="n"/>
       <c r="D6" s="41" t="inlineStr">
         <is>
-          <t>MMS test on cube domain (h = 1.0, 0.5, 0.25 mm); L2 error norms 2.5e-2, 6.3e-3, 1.6e-3; observed order 1.98. Also laminar manufactured vortex and rotating Couette with source term in Fluent (order 1.95–2.01). Taylor–Couette rotating-frame benchmark: torque within 1.2% of analytical at Re = 200.</t>
+          <t>Three time-step sizes (2e-4, 1e-4, 5e-5 s) evaluated for domain-averaged hemolysis damage at 2400 rpm/4 L/min; target ≤ 3% error relative to smallest step.</t>
         </is>
       </c>
       <c r="E6" s="41" t="inlineStr">
         <is>
-          <t>Analytical manufactured solution; analytical Taylor–Couette torque</t>
+          <t>Smallest time step (5e-5 s) as reference</t>
         </is>
       </c>
       <c r="F6" s="41" t="inlineStr">
@@ -2455,7 +2469,7 @@
       <c r="G6" s="33" t="n"/>
       <c r="H6" s="41" t="inlineStr">
         <is>
-          <t>Observed spatial order 1.95–2.01 (target ~2); Taylor–Couette torque error 1.2%</t>
+          <t>Δt = 2e-4 s: +6.4% error; Δt = 1e-4 s: +2.1% error; Δt = 1e-4 s selected as acceptable; pre-specified target &lt; 5%.</t>
         </is>
       </c>
       <c r="I6" s="42" t="inlineStr">
@@ -2467,7 +2481,7 @@
     <row r="7" ht="15" customHeight="1" s="18">
       <c r="A7" s="41" t="inlineStr">
         <is>
-          <t>Independent analyst rerun (use-error / reproducibility check)</t>
+          <t>Manufactured Solution Verification (Code Order Test)</t>
         </is>
       </c>
       <c r="B7" s="41" t="inlineStr">
@@ -2478,12 +2492,12 @@
       <c r="C7" s="33" t="n"/>
       <c r="D7" s="41" t="inlineStr">
         <is>
-          <t>Separate analyst independently re-meshed (snappyHexMesh) and reran the 3000 rpm/4 L/min case. Head matched primary result within 1.1%; shear hotspot Dice coefficient 0.83 on iso-τ = 300 Pa surfaces. Hardware determinism check: two clusters/compilers differed &lt; 0.2% in head and &lt; 3% in NIH.</t>
+          <t>Method of manufactured solutions on cube domain with grid spacings h = {1.0, 0.5, 0.25} mm; L2 error norms computed; observed spatial order verified against theoretical second-order expectation.</t>
         </is>
       </c>
       <c r="E7" s="41" t="inlineStr">
         <is>
-          <t>Primary analyst CFD result (artifact ACFD-221)</t>
+          <t>Analytical manufactured solution; expected order 2.0</t>
         </is>
       </c>
       <c r="F7" s="41" t="inlineStr">
@@ -2494,7 +2508,7 @@
       <c r="G7" s="33" t="n"/>
       <c r="H7" s="41" t="inlineStr">
         <is>
-          <t>Head difference 1.1%; Dice coefficient 0.83; cross-compiler NIH difference &lt; 3%</t>
+          <t>L2 errors: {2.5e-2, 6.3e-3, 1.6e-3}; observed order 1.98; rotating-frame Taylor-Couette benchmark torque within 1.2% of analytical at Re=200.</t>
         </is>
       </c>
       <c r="I7" s="42" t="inlineStr">
@@ -2718,12 +2732,12 @@
       </c>
       <c r="E5" s="42" t="inlineStr">
         <is>
-          <t>Commercial solver with documented QA; version-controlled environment; regression testing</t>
+          <t>Commercial solver with documented version control, regression testing, containerized environment, and independent reproducibility checks.</t>
         </is>
       </c>
       <c r="F5" s="41" t="inlineStr">
         <is>
-          <t>ANSYS CFX/Fluent 2024 R1 (commercial solvers with established QA). All meshes, case files, and post-processing scripts under Git LFS/DVC pinned at tag 3.4.7 with container hash. Python driver PumpRunner 2.3 automates case generation. Nightly regression on reduced geometry monitors head and torque for drift. Runs containerized on Ubuntu 22.04 with exact solver patches documented; Slurm/Intel MPI scripts archived. Hardware determinism verified across two clusters/compilers (&lt; 0.2% head, &lt; 3% NIH). Senior external SME reviewed mesh strategy and change requests fully implemented before final runs.</t>
+          <t>ANSYS CFX/Fluent 2024 R1 (commercial solvers) used; all case files and meshes under Git LFS/DVC pinned to tag 3.4.7 with container image (sha256 hash); Python driver PumpRunner 2.3 automates case generation; nightly regression suite on reduced geometry monitors head and torque drift; runs reproduced on two HPC clusters with different compilers (Intel oneAPI 2024 vs GCC 12) with &lt; 0.2% head difference; full artifact traceability via JAMA Connect J-COU-032 with immutable history; Slurm scripts and container recipe archived (appendix.md, report.md §9).</t>
         </is>
       </c>
       <c r="G5" s="41" t="inlineStr">
@@ -2751,12 +2765,12 @@
       </c>
       <c r="E6" s="42" t="inlineStr">
         <is>
-          <t>MMS or benchmark comparisons demonstrating correct order of accuracy for the governing equations</t>
+          <t>Observed spatial and temporal order consistent with theoretical expectations via MMS or analytical benchmark.</t>
         </is>
       </c>
       <c r="F6" s="41" t="inlineStr">
         <is>
-          <t>MMS tests performed in Fluent: laminar manufactured vortex and rotating Couette with source terms yielding observed spatial order 1.95–2.01 on poly meshes; temporal order ≈ 2.0 for unsteady manufactured field. Taylor–Couette rotating-frame benchmark at Re = 200 produced torque within 1.2% of analytical laminar solution. Grid spacing h = {1.0, 0.5, 0.25} mm cube test: L2 norms {2.5e-2, 6.3e-3, 1.6e-3}, observed order 1.98. CFX-vs-Fluent cross-code consistency check at 3000 rpm/4 L/min: head within 0.6% on matched meshes. Results documented in Appendix A and Section 4 of report.md and appendix.md.</t>
+          <t>Two MMS tests (laminar manufactured vortex and rotating Couette with source term) confirmed spatial order 1.95–2.01 on poly meshes and temporal order ≈ 2.0 for unsteady field. Rotating-frame Taylor-Couette benchmark produced torque within 1.2% of the analytical laminar solution at Re = 200. CFX and Fluent cross-checked at a common operating point (3000 rpm/4 L/min), head agreement 0.6% on matched meshes (report.md §4, appendix.md).</t>
         </is>
       </c>
       <c r="G6" s="41" t="inlineStr">
@@ -2784,12 +2798,12 @@
       </c>
       <c r="E7" s="42" t="inlineStr">
         <is>
-          <t>GCI &lt; 3% for head on fine mesh; time-step error &lt; 5% for NIH</t>
+          <t>Fine-grid GCI &lt; 3% for head; time-step error &lt; 5% for NIH; both pre-specified in Appendix D.</t>
         </is>
       </c>
       <c r="F7" s="41" t="inlineStr">
         <is>
-          <t>Three-mesh refinement study (7.9M/14.8M/28.6M cells) at 3000 rpm/4 L/min; observed order p ≈ 1.96; fine-grid GCI 0.9% (95%, Roache method) vs. pre-specified target &lt; 3% — passed. Time-step sensitivity for hemolysis (Δt = 2e-4/1e-4/5e-5 s): damage differences +6.4%/+2.1% relative to finest; Δt = 1e-4 s selected giving 2.1% error vs. target ≤ 3% — passed. Mesh quality metrics documented (min orthogonality 0.24, max non-orthogonal 54°, average y+ 0.7 on fine grid). Discretization contribution to head UQ &lt; 1% of total variance. Full details in Appendices A and D and Section 4.</t>
+          <t>Three-mesh refinement study (7.9M/14.8M/28.6M cells) at 3000 rpm/4 L/min; observed spatial order 1.96; fine-grid GCI 0.9% (95% confidence, Roache's method) — well within the 3% target. Time-step study (2e-4/1e-4/5e-5 s) for hemolysis: 2.1% error at selected Δt = 1e-4 s — within 5% target. Discretization contributes &lt; 1% to total UQ interval width for head. (report.md §4, §7, Appendix A, Appendix D).</t>
         </is>
       </c>
       <c r="G7" s="41" t="inlineStr">
@@ -2810,19 +2824,19 @@
         </is>
       </c>
       <c r="C8" s="41" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D8" s="41" t="n">
         <v>4</v>
       </c>
       <c r="E8" s="42" t="inlineStr">
         <is>
-          <t>Scaled residuals below 1e-6; mass/energy imbalance &lt; 0.1%; integral monitor stabilized</t>
+          <t>Scaled residuals below 1e-6; mass/energy imbalance &lt; 0.1%; integral QoI stable over final iterations.</t>
         </is>
       </c>
       <c r="F8" s="41" t="inlineStr">
         <is>
-          <t>Steady MRF runs: scaled residuals (momentum, continuity, turbulence) below 1e-6; hemolysis scalar below 1e-7; mass imbalance &lt; 0.04%; kinetic-energy imbalance &lt; 0.2%; head H stabilized to &lt; 0.05% over last 200 iterations (1450 total). Transient sliding-mesh runs: sub-iterations 10–15 per time step reducing residuals below 1e-5; phase-averaged NIH repeatability over last 4 of 12 rotor passes within 1.8%. Detailed logs provided in Appendix A (report.md) and Appendix E (appendix.md).</t>
+          <t>Steady runs: all scaled residuals (momentum, continuity, turbulence) below 1e-6; mass imbalance 0.04%; integral head stabilized within 0.05% over last 200 iterations (1450 total iterations at 3000 rpm/4 L/min). Transient runs: sub-iterations 10–15 per step reducing residuals below 1e-5; phase-averaged NIH consistent within 1.8% over last 4 of 12 rotor passes. Hemolysis scalar residuals below 1e-7. (report.md §4, appendix.md).</t>
         </is>
       </c>
       <c r="G8" s="41" t="inlineStr">
@@ -2846,16 +2860,16 @@
         <v>4</v>
       </c>
       <c r="D9" s="41" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E9" s="42" t="inlineStr">
         <is>
-          <t>Independent review of setup; boundary condition verification; mesh quality checks; reproducible pipeline</t>
+          <t>Independent setup review and rerun; boundary condition verification; mesh quality checks by separate analyst; SME review with documented change requests.</t>
         </is>
       </c>
       <c r="F9" s="41" t="inlineStr">
         <is>
-          <t>Case setup by Analyst A, mesh by Analyst B (specialist), independent full rerun by Analyst C from separate team (head within 1.1%, Dice 0.83 on shear hotspots). External senior turbomachinery SME (Engineer E, not on program) reviewed mesh strategy, y+ maps, and convergence; issued two change requests (near-shaft prism layers; curvature correction) both implemented before final runs. Python driver PumpRunner 2.3 and containerized pipeline reduce manual transcription errors. All boundary condition rationales archived with artifact IDs (Appendix C). Pre-specified acceptance targets recorded in Appendix D prior to any comparison (JAMA J-COU-032 with immutable history).</t>
+          <t>Case setup (Analyst A), mesh build (Analyst B), and independent rerun (Analyst C from separate team) with independently meshed grid (snappyHexMesh) — head matched within 1.1%; shear hotspot Dice coefficient 0.83. Experimental lead (Engineer D) not involved in CFD. External turbomachinery SME (SME E) reviewed mesh strategy, y+ maps, and convergence; issued two change requests (near-shaft prism layers; curvature correction) both implemented before final runs. Hardware determinism verified across two compiler environments. (report.md §9, appendix.md Appendix G).</t>
         </is>
       </c>
       <c r="G9" s="41" t="inlineStr">
@@ -2879,16 +2893,16 @@
         <v>4</v>
       </c>
       <c r="D10" s="41" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E10" s="42" t="inlineStr">
         <is>
-          <t>Governing equations and closure choices justified; known limitations documented; model-form sensitivity quantified</t>
+          <t>Governing equation choices justified; turbulence model selection documented; hemolysis model limitations acknowledged; model-form sensitivity quantified.</t>
         </is>
       </c>
       <c r="F10" s="41" t="inlineStr">
         <is>
-          <t>Incompressible isothermal Navier–Stokes with MRF/sliding-mesh justified for low-Mach (tip Mach &lt; 0.005) turbomachinery. k-ω SST with Spalart–Shur curvature correction selected with rationale; y+ ≤ 1 wall treatment. Model-form sensitivity explored: (i) Newtonian vs. Carreau–Yasuda (rheology branch); (ii) Giersiepen vs. Heuser–Opitz damage coefficients (±9–12% NIH bias); (iii) LES WALE spot check at 42M cells showing time-averaged H within 0.8% of RANS but peak shear 5–10% higher in tip leakage — used to inflate upper NIH uncertainty by 10%. Transitional flow not modeled (acknowledged worst outlier at low speed/flow). Cavitation omitted with NPSHr margin justification (&gt; 30 kPa). Single-temperature assumption justified by &lt; 0.5 °C bench temperature rise. Platelet activation and sublethal damage not captured; model restricted to ranking use only. Limitations clearly documented in Section 11.</t>
+          <t>Incompressible isothermal NS with MRF/sliding mesh justified for operating Re and Mach &lt; 0.005. k-ω SST with Spalart-Shur curvature correction selected with y+ ≤ 1; transitional effects acknowledged as a known gap at low flow. Two hemolysis coefficient sets (Giersiepen and Heuser-Opitz) used as model-form sensitivity; LES spot check (42M cells, WALE) confirmed time-averaged H within 0.8% of RANS and identified possible high-shear tail (+5–10% peak shear in tip leakage), incorporated as 10% NIH upper-interval inflation. Carreau-Yasuda vs Newtonian sensitivity noted. Limitations (no cavitation, no thermo-viscous heating, no platelet/sublethal damage) explicitly documented in §11. (report.md §2, §8, §11, Appendix F).</t>
         </is>
       </c>
       <c r="G10" s="41" t="inlineStr">
@@ -2916,12 +2930,12 @@
       </c>
       <c r="E11" s="42" t="inlineStr">
         <is>
-          <t>Material properties and boundary conditions characterized with uncertainty; geometry verified against as-built parts</t>
+          <t>Material properties from measurement with uncertainty bounds; geometry from production CAD with CMM verification; boundary conditions traceable to calibrated instruments; epistemic/aleatory distinction documented.</t>
         </is>
       </c>
       <c r="F11" s="41" t="inlineStr">
         <is>
-          <t>Fluid properties: density 1050 kg/m³ at 37 °C; Carreau–Yasuda parameters with ±10% on μ∞ and ±15% on λ from fluid lab sheets; Newtonian branch 3.5 cP matched to rig fluid. Rotor speed tolerance ±10 rpm from vendor tachometer calibration. Tip clearance 60–100 μm range from metrology reports (nominal 80 μm per assembly measurement); incorporated into tolerance sweep. Blade fillet radius ±0.05 mm. Inflow turbulence intensity 5% ± 2% (triangular distribution). Geometry from production CAD Rev E-17; CMM reports confirmed &lt; 30 μm deviation on key features. Damage model epistemic parameters (C, α) characterized with literature range and fitted alternate set; aleatory/epistemic distinction noted. Morris screening identified dominant inputs; Sobol' indices quantified (S_tip ≈ 0.41, S_μ ≈ 0.27 for H; S_α ≈ 0.38, S_tip ≈ 0.31 for NIH).</t>
+          <t>Blood rheology (Carreau-Yasuda parameters) with ±10% uncertainty on μ∞ and ±15% on λ from fluid lab sheets; density 1050 kg/m³ at 37 °C. Tip clearance 80 μm per measured assembly; tolerance sweep 60–100 μm from metrology reports. Rotor speed ±10 rpm from vendor tachometer calibration. Inflow turbulence 5% ± 2% (triangular distribution). Blade-to-hub fillet ±0.05 mm. CAD geometry matched CMM reports within 30 μm on key features. Epistemic (damage coefficients) vs aleatory (viscosity donor variation) distinction noted. Morris screening and Sobol' first-order indices quantified input importance. (report.md §3, §7).</t>
         </is>
       </c>
       <c r="G11" s="41" t="inlineStr">
@@ -2949,12 +2963,12 @@
       </c>
       <c r="E12" s="42" t="inlineStr">
         <is>
-          <t>Production-representative test articles; adequate sample count; statistical characterization</t>
+          <t>Multiple specimens/test days; statistically characterized variability; production-representative test articles; sample size provides adequate statistical power.</t>
         </is>
       </c>
       <c r="F12" s="41" t="inlineStr">
         <is>
-          <t>Hydraulic rig tests used the Rev E pump (same production CAD; CMM-verified &lt; 30 μm on key features). Blood-loop tests used triplicates on separate days for each of three design variants (Rev D, E, E+) across three flow rates — nine total NIH conditions with CV 6.1% across triplicates. Bovine blood Hct 38–42% (target 40%); temperature 36.8–37.2 °C. Only one pump unit described for each variant; sample size per condition is n = 3 (triplicates). Upper speed (3600 rpm) not tested in blood due to sample limitations. Experimental lead (Engineer D) was independent from CFD team.</t>
+          <t>Hydraulic tests: 3 test days at reference point (3000 rpm/4 L/min), day-to-day variability 0.9% (1σ); 15 operating points total across all speeds/flows on production Rev E hardware. Blood-loop NIH: triplicates on separate days; CV 6.1%; bovine blood Hct 38–42% (n=9 conditions total across 3 flow rates, 3 design variants). CMM confirmation of test hardware within 30 μm. Sample size is adequate for ranking purposes but limited (only 2400 rpm tested in blood due to sample limitations), constraining NIH coverage. (report.md §5, Appendix B).</t>
         </is>
       </c>
       <c r="G12" s="41" t="inlineStr">
@@ -2982,12 +2996,12 @@
       </c>
       <c r="E13" s="42" t="inlineStr">
         <is>
-          <t>Calibrated instruments with traceable uncertainty; controlled environment; recognized test standards followed</t>
+          <t>Calibrated instrumentation traceable to national standards; controlled environment; measurement uncertainty quantified; tests conducted per recognized standards (ISO 7199, ASTM F1841).</t>
         </is>
       </c>
       <c r="F13" s="41" t="inlineStr">
         <is>
-          <t>Hydraulic tests per ISO 7199; Rosemount 3051 differential transducers calibrated within 30 days, as-left check within 0.02% span (±0.075% span accuracy); Transonic clamp-on flowmeter ±2%, factory calibration traceable to NIST. Repeatability across three test days: H CV 0.9% (1σ) at 3000 rpm/4 L/min. Blood-loop per ASTM F1841; temperature control ±0.2 °C; degassing to 40% saturation; no visible bubbles. NIH sampling and plasma-free hemoglobin computation per standard protocol. Raw CSV files and calibration certs archived with artifact IDs (Appendix C). Lab temperature 36.8–37.2 °C consistent with 37 °C model assumption.</t>
+          <t>Hydraulic tests per ISO 7199; Rosemount 3051 differential transducers calibrated within 30 days pre-test, as-left check within 0.02% span (±0.075% span accuracy); Transonic clamp-on flowmeter factory-calibrated traceable to NIST (±2%). Temperature control ±0.2 °C; degassing to 40% saturation; no visible bubbles. Blood-loop NIH per ASTM F1841; temperature 36.8–37.2 °C; lab temperature controlled. Hydraulic repeatability 0.9% (1σ); NIH CV 6.1%. (report.md §5, Appendix B).</t>
         </is>
       </c>
       <c r="G13" s="41" t="inlineStr">
@@ -3015,12 +3029,12 @@
       </c>
       <c r="E14" s="42" t="inlineStr">
         <is>
-          <t>CFD boundary conditions demonstrably matched to experimental conditions; input discrepancies quantified</t>
+          <t>Model inputs demonstrably matched to experimental conditions; rheology alignment documented; geometry consistency confirmed; measurement uncertainty propagated into comparison.</t>
         </is>
       </c>
       <c r="F14" s="41" t="inlineStr">
         <is>
-          <t>Hydraulic comparison used Newtonian μ = 3.5 cP in CFD to match rig fluid (water–glycerol tuned to high-shear viscosity at 37 °C), explicitly avoiding rheology confounding. For hemolysis, Carreau–Yasuda CFD output post-processed to NIH via same power-law surrogate as bench metric (ASTM F1841 protocol). Non-dimensional similarity verified: impeller Reynolds number within ±5% across matched points; blade tip Mach &lt; 0.005; Strouhal &lt; 0.02. Geometry: CMM-confirmed &lt; 30 μm deviation on key features; tip clearance set to 80 μm per assembly measurement and varied 60–100 μm in sensitivity. Rotor speed ±10 rpm. Temperature 37 °C (bench 36.8–37.2 °C). Each plotted point linked to artifact ID (Appendix C).</t>
+          <t>For H-Q comparison, CFD explicitly run with Newtonian μ = 3.5 cP to match rig fluid (water-glycerol), eliminating rheology confounding. For NIH comparison, CFD used Carreau model and post-processed via power-law surrogate to NIH for direct metric alignment with ASTM F1841 bench output. Tip clearance set to measured 80 μm with ±20 μm sweep; CAD-to-CMM delta &lt; 30 μm incorporated in tolerance sweep. Rotor speed, temperature, and flow conditions matched one-to-one between CFD runs and lab protocol. Non-dimensional group comparison (Re within ±5%, Ma &lt; 0.005, St &lt; 0.02) confirms flow regime equivalence. (report.md §5, §6).</t>
         </is>
       </c>
       <c r="G14" s="41" t="inlineStr">
@@ -3048,12 +3062,12 @@
       </c>
       <c r="E15" s="42" t="inlineStr">
         <is>
-          <t>Quantitative error metrics against pre-specified thresholds; multiple comparison points; uncertainty bands reported</t>
+          <t>Quantitative metrics (MAPE, bias, RMSE) against pre-specified thresholds; multiple comparison points; UQ intervals reported alongside comparisons; ranking fidelity assessed.</t>
         </is>
       </c>
       <c r="F15" s="41" t="inlineStr">
         <is>
-          <t>Hydraulic: 15 operating points; pre-specified thresholds (pointwise &lt; 5%, MAPE &lt; 4%) declared before comparison (JAMA J-COU-032); achieved MAPE 2.7%, worst case 4.9% — both targets met. H-Q curve slopes matched within 3%. 95% head interval [108.2, 112.7] mmHg (median 110.4) from LHC propagation. NIH: 9 bench conditions; bias +24% (baseline) / +12% (alternate coefficients); correct ranking across three designs; 5/9 conditions bracketed by 95% CFD interval; experimental triplicates (0.029, 0.031, 0.032 g/100 L) vs. CFD median 0.035; pre-specified target &lt; 30% error and correct ranking — met on average (two points at 5 L/min marginally exceeded 30% with baseline coefficients, documented with justification in JAMA). NIH ranking tie at 5 L/min (E vs. E+) documented as deviation with bench tie-breaker.</t>
+          <t>Hydraulic: MAPE 2.7% (target &lt; 4%), worst-case 4.9% (target &lt; 5%), H-Q slope within 3% — all pre-specified targets met across 15 points. NIH: bias +24% (baseline) / +12% (alternate coefficients) against &lt; 30% target; RMSE 0.010 g/100 L; correct ranking in 3/3 design variants; 5/9 conditions bracketed by 95% UQ interval; two 5 L/min points marginally exceeded 30% with baseline coefficients (documented deviation). 95% head interval [108.2, 112.7] mmHg and NIH interval [0.026, 0.044] g/100 L reported. All thresholds pre-declared in Appendix D before any comparisons. (report.md §5, §7, §13, Appendix D).</t>
         </is>
       </c>
       <c r="G15" s="41" t="inlineStr">
@@ -3081,12 +3095,12 @@
       </c>
       <c r="E16" s="42" t="inlineStr">
         <is>
-          <t>QoIs directly measure the safety/performance concern and are measurable both computationally and experimentally</t>
+          <t>QoIs directly address the engineering decisions (firmware guard bands, design ranking); measurable both computationally and experimentally; link to downstream patient safety consequence documented.</t>
         </is>
       </c>
       <c r="F16" s="41" t="inlineStr">
         <is>
-          <t>Head (H-Q map) directly governs firmware speed-limiter curves and battery sizing — the primary engineering decision. NIH directly indexes blood damage potential and is the standard metric for screening hemolysis (ASTM F1841). Both QoIs are computed by the CFD model and measured in the corresponding bench tests using the same definitions (pressure rise across pump; NIH per ASTM F1841), enabling direct comparison. Sensitivity analysis (Morris + Sobol') confirms dominant physical drivers are captured in both QoIs. The applicability of NIH as a clinical safety endpoint is explicitly bounded: it is used for ranking and screening, not for absolute clinical claims.</t>
+          <t>Head (H) directly feeds firmware speed-limiter curves and battery sizing — measurable by both CFD (integral pressure rise) and differential pressure transducer in rig. NIH is a recognized standardized metric (ASTM F1841) measurable in both CFD post-processing (via pathline integration and power-law surrogate) and blood-loop assay. Decision impact of errors is documented: H error &gt; ~5% could mis-set controller limits with moderate-to-high clinical consequence; NIH mis-ranking affects schedule/cost and indirectly safety. The distinction between screening use (NIH) and direct firmware use (H) is explicitly stated, calibrating the level of scrutiny appropriately. (report.md §1, §12).</t>
         </is>
       </c>
       <c r="G16" s="41" t="inlineStr">
@@ -3114,12 +3128,12 @@
       </c>
       <c r="E17" s="42" t="inlineStr">
         <is>
-          <t>Validation conditions cover the full intended operating envelope; same geometry, physics regime, and fluid; gaps identified and bounded</t>
+          <t>Validation conditions span the full intended operating envelope (2–6 L/min, 2400–3600 rpm, Hct 35–45%, 36–38 °C); geometry matches production hardware; gaps identified and risk-bounded.</t>
         </is>
       </c>
       <c r="F17" s="41" t="inlineStr">
         <is>
-          <t>Hydraulic validation covers all three speeds (2400/3000/3600 rpm) and all five flow rates (2–6 L/min) — full COU envelope tested one-to-one. NIH validation covers only 2400 rpm (one of three intended speeds) and three flow rates; 3000 and 3600 rpm blood-loop data absent due to sample limitations — a documented gap. Extrapolation to higher speeds involves uncertainty in damage law exponent at different shear levels and residence times. Geometry: as-tested Rev E parts with CMM verification. Fluid: rig used water–glycerol matched to high-shear viscosity; blood-loop used bovine blood Hct 38–42% (COU is Hct 35–45%) — minor gap noted. Operating Reynolds numbers within ±5%; Mach and Strouhal numbers confirm same flow regime. Transitional effects at lowest operating point (2 L/min/2400 rpm) not fully captured. Limitations and extrapolation risks documented in Sections 6 and 11.</t>
+          <t>Hydraulic validation covers all three speeds and all five flow rates — full COU envelope. NIH validation covers only 2400 rpm (not 3000 or 3600 rpm) and three flow rates due to blood sample limitations; extrapolation to higher speeds involves uncertainty in damage law exponent at different shear/residence time conditions. Geometry used in CFD matches as-tested parts (CMM within 30 μm). Similarity checks (Re within ±5%) confirm comparable flow regime. Gaps explicitly acknowledged: (1) NIH at 3000/3600 rpm untested in blood; (2) transitional flow at &lt; 2 L/min not covered; (3) cavitation not modeled (margin &gt; 30 kPa justified). These gaps are documented with residual risk characterization and recommendations for extension if COU expands. (report.md §6, §11).</t>
         </is>
       </c>
       <c r="G17" s="41" t="inlineStr">
@@ -3208,7 +3222,7 @@
       </c>
       <c r="B3" s="39" t="inlineStr">
         <is>
-          <t>The CFD model LVAD-CFD-hem_v3.4 is accepted for its two stated contexts of use subject to documented conditions. For the hydraulic H-Q map: all pre-specified acceptance criteria were met (MAPE 2.7% &lt; 4%; all points within 5% except the documented worst-case 4.9% at 2 L/min/2400 rpm; fine-mesh GCI 0.9% &lt; 3%; independent rerun within 1.1%). The model is fit to set firmware speed-limiter curves and size the battery pack within the 2–6 L/min, 2400–3600 rpm envelope. For NIH screening: pre-specified criteria were met on average (bias &lt; 30%; correct design ranking across Rev D/E/E+); two points at 5 L/min marginally exceeded the 30% threshold with baseline coefficients and are documented with justification. The model is accepted for design ranking and screening gate decisions only — not for absolute clinical hemolysis claims or patient risk quantification. Conditions recorded: (1) if operation below 2 L/min is contemplated, a transitional turbulence model (γ–Reθ) must be incorporated; (2) blood-loop validation at 3000 and 3600 rpm should be obtained before extending NIH screening to those speeds; (3) cavitation modeling is required if inlet pressures fall within 30 kPa of NPSHr; (4) NIH results must not be used to set absolute clinical safety limits without in vitro and in vivo data; (5) NIH ranking tie between Rev E and E+ at 5 L/min is resolved by bench data (E+ favored) and is recorded in JAMA J-COU-032.</t>
+          <t>The LVAD-CFD-hem_v3.4 model meets all pre-specified acceptance criteria for both quantities of interest. For the hydraulic H-Q map: fine-grid GCI of 0.9% is well below the 3% numerical target; MAPE of 2.7% and worst-case point error of 4.9% satisfy the &lt; 4% and &lt; 5% thresholds across all 15 validation points; the model is accepted for setting firmware speed-limiter curves and battery sizing margins. For NIH screening: bias of +24% (baseline coefficients) and +12% (alternate) remain within the pre-declared &lt; 30% absolute threshold; correct design ranking is preserved across all three variants; the marginal exceedance at two 5 L/min points with baseline coefficients is documented as a deviation and accepted given that the alternate coefficient set resolves it and the NIH result is used for ranking/screening only, not for direct patient safety claims. Conditions carried forward: (1) NIH model must not be used to set absolute clinical safety limits or for patient risk claims — in vitro/in vivo data required for that purpose; (2) if operating envelope extends below 2 L/min, a transitional turbulence model (γ–Reθ) should be incorporated; (3) if lower inlet pressures are contemplated, cavitation modeling must be added; (4) NIH predictions at 3000 and 3600 rpm remain extrapolations — blood-loop testing at those speeds is recommended before any expanded COU claim.</t>
         </is>
       </c>
       <c r="C3" s="22" t="inlineStr">
